--- a/Filtered/HCA_Florida_Mercy_Hospital.xlsx
+++ b/Filtered/HCA_Florida_Mercy_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1306,6 +1361,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1862,6 +1957,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1919,6 +2019,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2708,6 +2868,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2842,6 +3012,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2976,6 +3156,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3038,6 +3223,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3095,6 +3285,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3172,6 +3367,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3229,6 +3429,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3363,6 +3573,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3497,6 +3717,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3631,6 +3861,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3765,6 +4005,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3976,6 +4231,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4110,6 +4375,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4244,6 +4519,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4378,6 +4663,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4512,6 +4807,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4589,6 +4889,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4646,6 +4951,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4723,6 +5033,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4780,6 +5095,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4857,6 +5177,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4914,6 +5239,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4991,6 +5321,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5048,6 +5383,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5125,6 +5465,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5182,6 +5527,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5259,6 +5609,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5316,6 +5671,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5393,6 +5753,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5470,6 +5835,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5527,6 +5897,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5604,6 +5979,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5661,6 +6041,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5723,6 +6108,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5780,6 +6170,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5857,6 +6252,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5914,6 +6314,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5991,6 +6396,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6048,6 +6458,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6125,6 +6540,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6182,6 +6602,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6259,6 +6684,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6316,6 +6746,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6393,6 +6828,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6450,6 +6890,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6527,6 +6972,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6584,6 +7034,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6661,6 +7116,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6718,6 +7178,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6795,6 +7260,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6852,6 +7322,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6929,6 +7404,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6986,6 +7466,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7063,6 +7548,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7120,6 +7610,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7197,6 +7692,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7254,6 +7754,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7331,6 +7836,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7388,6 +7898,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7465,6 +7980,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7522,6 +8042,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7599,6 +8124,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7656,6 +8186,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7733,6 +8268,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7790,6 +8330,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7867,6 +8412,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7924,6 +8474,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8001,6 +8556,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8058,6 +8618,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8135,6 +8700,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8192,6 +8762,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8269,6 +8844,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8326,6 +8906,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8403,6 +8988,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8480,6 +9070,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8537,6 +9132,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8614,6 +9214,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8691,6 +9296,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8748,6 +9358,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8825,6 +9440,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8882,6 +9502,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8959,6 +9584,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9036,6 +9666,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9093,6 +9728,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9170,6 +9810,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9227,6 +9872,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9304,6 +9954,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9381,6 +10036,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9438,6 +10098,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9515,6 +10180,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9572,6 +10242,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9649,6 +10324,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9706,6 +10386,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9783,6 +10468,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9840,6 +10530,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9902,6 +10597,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9959,6 +10659,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10021,6 +10726,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10083,6 +10793,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10140,6 +10855,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10217,6 +10937,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10274,6 +10999,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10351,6 +11081,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10408,6 +11143,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10485,6 +11225,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10542,6 +11287,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10619,6 +11369,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10676,6 +11431,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10753,6 +11513,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10810,6 +11575,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10887,6 +11657,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10944,6 +11719,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11021,6 +11801,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11078,6 +11863,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11155,6 +11945,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11212,6 +12007,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11289,6 +12089,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11346,6 +12151,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11423,6 +12233,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11480,6 +12295,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11557,6 +12377,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11614,6 +12439,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11691,6 +12521,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11748,6 +12583,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11825,6 +12665,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11882,6 +12727,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11959,6 +12809,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12016,6 +12871,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12093,6 +12953,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12170,6 +13035,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12227,6 +13097,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12304,6 +13179,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12361,6 +13241,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12423,6 +13308,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12480,6 +13370,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12542,6 +13437,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12599,6 +13499,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12661,6 +13566,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12718,6 +13628,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12795,6 +13710,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12852,6 +13772,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12929,6 +13854,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12986,6 +13916,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13063,6 +13998,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13120,6 +14060,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13197,6 +14142,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13254,6 +14204,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13331,6 +14286,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13388,6 +14348,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13465,6 +14430,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13522,6 +14492,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13599,6 +14574,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13656,6 +14636,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13733,6 +14718,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13790,6 +14780,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13867,6 +14862,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13924,6 +14924,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14001,6 +15006,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14058,6 +15068,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14135,6 +15150,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14192,6 +15212,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14269,6 +15294,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14326,6 +15356,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14403,6 +15438,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14460,6 +15500,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14537,6 +15582,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14594,6 +15644,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14671,6 +15726,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14728,6 +15788,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14805,6 +15870,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14862,6 +15932,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14939,6 +16014,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14996,6 +16076,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15073,6 +16158,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15130,6 +16220,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15207,6 +16302,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15264,6 +16364,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15341,6 +16446,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15398,6 +16508,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15475,6 +16590,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15532,6 +16652,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15609,6 +16734,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15666,6 +16796,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15743,6 +16878,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15800,6 +16940,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15877,6 +17022,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15934,6 +17084,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16011,6 +17166,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16068,6 +17228,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16145,6 +17310,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16202,6 +17372,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16279,6 +17454,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16336,6 +17516,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16413,6 +17598,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16470,6 +17660,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16532,6 +17727,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16589,6 +17789,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16666,6 +17871,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16723,6 +17933,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16800,6 +18015,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16857,6 +18077,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16934,6 +18159,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16991,6 +18221,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17068,6 +18303,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17125,6 +18365,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17202,6 +18447,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17279,6 +18529,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17336,6 +18591,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17413,6 +18673,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17470,6 +18735,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17547,6 +18817,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17604,6 +18879,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17681,6 +18961,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17738,6 +19023,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17815,6 +19105,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17872,6 +19167,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17949,6 +19249,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18006,6 +19311,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18083,6 +19393,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18140,6 +19455,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18217,6 +19537,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18274,6 +19599,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18351,6 +19681,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18408,6 +19743,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18485,6 +19825,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18542,6 +19887,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18619,6 +19969,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18676,6 +20031,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18753,6 +20113,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18810,6 +20175,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18887,6 +20257,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18944,6 +20319,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19021,6 +20401,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19078,6 +20463,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19155,6 +20545,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19212,6 +20607,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19289,6 +20689,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19346,6 +20751,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19423,6 +20833,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19480,6 +20895,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19557,6 +20977,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19614,6 +21039,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19691,6 +21121,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19748,6 +21183,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19825,6 +21265,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19882,6 +21327,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19959,6 +21409,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20016,6 +21471,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20093,6 +21553,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20150,6 +21615,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20227,6 +21697,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20284,6 +21759,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20361,6 +21841,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20418,6 +21903,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20495,6 +21985,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20552,6 +22047,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20629,6 +22129,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20686,6 +22191,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20763,6 +22273,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20820,6 +22335,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20897,6 +22417,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20974,6 +22499,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21031,6 +22561,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21108,6 +22643,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21165,6 +22705,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21242,6 +22787,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21299,6 +22849,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21376,6 +22931,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21433,6 +22993,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21510,6 +23075,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21587,6 +23157,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21644,6 +23219,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21721,6 +23301,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21778,6 +23363,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21855,6 +23445,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21932,6 +23527,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21989,6 +23589,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22066,6 +23671,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22123,6 +23733,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22200,6 +23815,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22257,6 +23877,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22334,6 +23959,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22391,6 +24021,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22468,6 +24103,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22525,6 +24165,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22602,6 +24247,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22659,6 +24309,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22736,6 +24391,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22793,6 +24453,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22865,6 +24530,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22922,6 +24592,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22999,6 +24674,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23076,6 +24756,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23133,6 +24818,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23210,6 +24900,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23267,6 +24962,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23344,6 +25044,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23401,6 +25106,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23478,6 +25188,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23535,6 +25250,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23597,6 +25317,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23654,6 +25379,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23731,6 +25461,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23788,6 +25523,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23865,6 +25605,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23922,6 +25667,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23999,6 +25749,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24056,6 +25811,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24118,6 +25878,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24175,6 +25940,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24252,6 +26022,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24309,6 +26084,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24386,6 +26166,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24443,6 +26228,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24505,6 +26295,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24562,6 +26357,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24639,6 +26439,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24696,6 +26501,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24773,6 +26583,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24830,6 +26645,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24907,6 +26727,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24964,6 +26789,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25041,6 +26871,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25098,6 +26933,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25175,6 +27015,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25232,6 +27077,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25294,6 +27144,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25351,6 +27206,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25428,6 +27288,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25485,6 +27350,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25562,6 +27432,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25619,6 +27494,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25696,6 +27576,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25753,6 +27638,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25830,6 +27720,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25887,6 +27782,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25964,6 +27864,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26021,6 +27926,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26098,6 +28008,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26155,6 +28070,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26232,6 +28152,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26289,6 +28214,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26366,6 +28296,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26423,6 +28358,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26485,6 +28425,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26542,6 +28487,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26619,6 +28569,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26676,6 +28631,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26753,6 +28713,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26810,6 +28775,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26887,6 +28857,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26944,6 +28919,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27021,6 +29001,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27078,6 +29063,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27155,6 +29145,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27212,6 +29207,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27289,6 +29289,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27346,6 +29351,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27423,6 +29433,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27480,6 +29495,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27557,6 +29577,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27614,6 +29639,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27691,6 +29721,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27748,6 +29783,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27825,6 +29865,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27882,6 +29927,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27959,6 +30009,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28016,6 +30071,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28093,6 +30153,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28150,6 +30215,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28227,6 +30297,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28284,6 +30359,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28361,6 +30441,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28418,6 +30503,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28480,6 +30570,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28542,6 +30637,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28604,6 +30704,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28661,6 +30766,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28738,6 +30848,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28795,6 +30910,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28857,6 +30977,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28919,6 +31044,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28981,6 +31111,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29043,6 +31178,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29105,6 +31245,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29162,6 +31307,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29239,6 +31389,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29296,6 +31451,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29373,6 +31533,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29430,6 +31595,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29507,6 +31677,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29564,6 +31739,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29641,6 +31821,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29698,6 +31883,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29760,6 +31950,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29822,6 +32017,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29884,6 +32084,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29941,6 +32146,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30018,6 +32228,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30075,6 +32290,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30152,6 +32372,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30209,6 +32434,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30271,6 +32501,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30328,6 +32563,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30390,6 +32630,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30452,6 +32697,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30509,6 +32759,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30571,6 +32826,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30633,6 +32893,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30695,6 +32960,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30752,6 +33022,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30829,6 +33104,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30886,6 +33166,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30948,6 +33233,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31010,6 +33300,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31072,6 +33367,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31129,6 +33429,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31206,6 +33511,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31263,6 +33573,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31325,6 +33640,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31382,6 +33702,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31459,6 +33784,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31516,6 +33846,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31578,6 +33913,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31640,6 +33980,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31702,6 +34047,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31759,6 +34109,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31836,6 +34191,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31893,6 +34253,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -31970,6 +34335,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32027,6 +34397,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32089,6 +34464,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32151,6 +34531,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32208,6 +34593,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32270,6 +34660,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32332,6 +34727,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32394,6 +34794,11 @@
           <t>COCMHB</t>
         </is>
       </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -32449,6 +34854,11 @@
       <c r="K483" t="inlineStr">
         <is>
           <t>COCMHB</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
